--- a/台股股票代碼NEW.xlsx
+++ b/台股股票代碼NEW.xlsx
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>富邦琤肭磪囓2</t>
+          <t>富邦恒生國企正2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>富邦琤肭磪齯1</t>
+          <t>富邦恒生國企反1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>富邦琤肭磪</t>
+          <t>富邦恒生國企</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>宏</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>倚天酷-創</t>
+          <t>倚天酷碁-創</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -29996,7 +29996,7 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>建</t>
+          <t>建碁</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -52364,7 +52364,7 @@
       </c>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>安</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C1668" t="inlineStr">
@@ -55180,7 +55180,7 @@
       </c>
       <c r="B1756" t="inlineStr">
         <is>
-          <t>啟</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C1756" t="inlineStr">
@@ -59788,7 +59788,7 @@
       </c>
       <c r="B1900" t="inlineStr">
         <is>
-          <t>安硌穈T</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C1900" t="inlineStr">
@@ -61100,7 +61100,7 @@
       </c>
       <c r="B1941" t="inlineStr">
         <is>
-          <t>展眥篕</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C1941" t="inlineStr">
@@ -61612,7 +61612,7 @@
       </c>
       <c r="B1957" t="inlineStr">
         <is>
-          <t>宏硌穈T</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C1957" t="inlineStr">
@@ -62988,7 +62988,7 @@
       </c>
       <c r="B2000" t="inlineStr">
         <is>
-          <t>宏砦C戲-創</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C2000" t="inlineStr">
@@ -66028,7 +66028,7 @@
       </c>
       <c r="B2095" t="inlineStr">
         <is>
-          <t>宏硒撥s</t>
+          <t>宏碁智新</t>
         </is>
       </c>
       <c r="C2095" t="inlineStr">
@@ -67660,7 +67660,7 @@
       </c>
       <c r="B2146" t="inlineStr">
         <is>
-          <t>洛</t>
+          <t>洛碁</t>
         </is>
       </c>
       <c r="C2146" t="inlineStr">
@@ -69548,7 +69548,7 @@
       </c>
       <c r="B2205" t="inlineStr">
         <is>
-          <t>矬</t>
+          <t>恒耀</t>
         </is>
       </c>
       <c r="C2205" t="inlineStr">
